--- a/data/databases/user_1786447244261.xlsx
+++ b/data/databases/user_1786447244261.xlsx
@@ -122,10 +122,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -157,10 +157,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:L30"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,16 +442,21 @@
         <v>Mumbai</v>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" t="str">
+        <v>test</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L30"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:L1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,7 +474,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/databases/user_1786447244261.xlsx
+++ b/data/databases/user_1786447244261.xlsx
@@ -5,6 +5,10 @@
   <sheets>
     <sheet name="Customers" sheetId="1" r:id="rId1"/>
     <sheet name="Orders" sheetId="2" r:id="rId2"/>
+    <sheet name="Users" sheetId="3" r:id="rId3"/>
+    <sheet name="Title" sheetId="4" r:id="rId4"/>
+    <sheet name="Heads" sheetId="5" r:id="rId5"/>
+    <sheet name="Kotak_Bank_1787732907953" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -122,10 +126,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -157,10 +161,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -477,4 +481,1457 @@
     <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>email</v>
+      </c>
+      <c r="D1" t="str">
+        <v>password</v>
+      </c>
+      <c r="E1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1787732889328</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Gautam</v>
+      </c>
+      <c r="C2" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>123456</v>
+      </c>
+      <c r="E2" t="str">
+        <v>2026-08-26T08:28:09.328Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>1787916675452</v>
+      </c>
+      <c r="B3" t="str">
+        <v>TEST USER</v>
+      </c>
+      <c r="C3" t="str">
+        <v>test@gmail.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>123456</v>
+      </c>
+      <c r="E3" t="str">
+        <v>2026-08-28T11:31:15.452Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title_name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>crt_by</v>
+      </c>
+      <c r="D1" t="str">
+        <v>crt_dt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1787732940100</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Kotak_Bank_1787732907953</v>
+      </c>
+      <c r="C2" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>2026-08-26T08:29:00.100Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>keywords</v>
+      </c>
+      <c r="E1" t="str">
+        <v>crt_by</v>
+      </c>
+      <c r="F1" t="str">
+        <v>crt_dt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1787733209207518</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Intrest</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Int.Pd</v>
+      </c>
+      <c r="E2" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>2026-08-26T08:33:29.207Z</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>1787733275852497</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Loan</v>
+      </c>
+      <c r="C3" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>2026-08-26T08:34:35.852Z</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>1787733307447759</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Food Exp</v>
+      </c>
+      <c r="C4" t="str">
+        <v>DR</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Food, JUMBO KING, Juse, Tungareshwar</v>
+      </c>
+      <c r="E4" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026-08-26T08:35:07.447Z</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>178773346666498</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Commodity Exp</v>
+      </c>
+      <c r="C5" t="str">
+        <v>DR</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Indian Railway, JIO, Transport Com</v>
+      </c>
+      <c r="E5" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2026-08-26T08:37:46.665Z</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>1787733556369812</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Divident</v>
+      </c>
+      <c r="C6" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D6" t="str">
+        <v>NACH</v>
+      </c>
+      <c r="E6" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-08-26T08:39:16.369Z</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>1787733656998177</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Self Given</v>
+      </c>
+      <c r="C7" t="str">
+        <v>DR</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Gautam, ANGEL</v>
+      </c>
+      <c r="E7" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-08-26T08:40:56.998Z</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>1787733674076245</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Self Recieved</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Gautam, ANGEL</v>
+      </c>
+      <c r="E8" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-08-26T08:41:14.076Z</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>1787735705310443</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="C9" t="str">
+        <v>CR</v>
+      </c>
+      <c r="D9" t="str">
+        <v>DIGITAL ADVANCED</v>
+      </c>
+      <c r="E9" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-08-26T09:15:05.310Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G50"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sr_no</v>
+      </c>
+      <c r="B1" t="str">
+        <v>txn_date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>value_date</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+      <c r="E1" t="str">
+        <v>chq_ref_no</v>
+      </c>
+      <c r="F1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="G1" t="str">
+        <v>dr_cr</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>01-04-2026 2:51:34</v>
+      </c>
+      <c r="C2" t="str">
+        <v>31-03-2026</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Int.Pd:8645700477:01-01-2026 to 31-03-2026</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v>35</v>
+      </c>
+      <c r="G2" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>30-03-2026 09:57:31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>30-03-2026</v>
+      </c>
+      <c r="D3" t="str">
+        <v>UPI/RISHIKESH RAMSI/608927382558/UPI</v>
+      </c>
+      <c r="E3" t="str">
+        <v>UPI-608941747929</v>
+      </c>
+      <c r="F3" t="str">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>29-03-2026 19:45:23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>29-03-2026</v>
+      </c>
+      <c r="D4" t="str">
+        <v>UPI/RITESH RAMKRIPA/608803184323/UPI</v>
+      </c>
+      <c r="E4" t="str">
+        <v>UPI-608812920930</v>
+      </c>
+      <c r="F4" t="str">
+        <v>50</v>
+      </c>
+      <c r="G4" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>29-03-2026 13:08:49</v>
+      </c>
+      <c r="C5" t="str">
+        <v>29-03-2026</v>
+      </c>
+      <c r="D5" t="str">
+        <v>UPI/Mr SAFAR  ALI/608875641203/UPI</v>
+      </c>
+      <c r="E5" t="str">
+        <v>UPI-608884500615</v>
+      </c>
+      <c r="F5" t="str">
+        <v>30</v>
+      </c>
+      <c r="G5" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>28-03-2026 20:54:33</v>
+      </c>
+      <c r="C6" t="str">
+        <v>28-03-2026</v>
+      </c>
+      <c r="D6" t="str">
+        <v>UPI/Mr SADASHIV GAN/608748935163/UPI</v>
+      </c>
+      <c r="E6" t="str">
+        <v>UPI-608749500962</v>
+      </c>
+      <c r="F6" t="str">
+        <v>30</v>
+      </c>
+      <c r="G6" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>27-03-2026 20:35:52</v>
+      </c>
+      <c r="C7" t="str">
+        <v>27-03-2026</v>
+      </c>
+      <c r="D7" t="str">
+        <v>UPI/JUMBO KING/608689585291/UPI</v>
+      </c>
+      <c r="E7" t="str">
+        <v>UPI-608677871790</v>
+      </c>
+      <c r="F7" t="str">
+        <v>357</v>
+      </c>
+      <c r="G7" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>27-03-2026 18:57:28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>27-03-2026</v>
+      </c>
+      <c r="D8" t="str">
+        <v>UPI/Indian Railways/608681370707/UPI</v>
+      </c>
+      <c r="E8" t="str">
+        <v>UPI-608668678728</v>
+      </c>
+      <c r="F8" t="str">
+        <v>95</v>
+      </c>
+      <c r="G8" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>27-03-2026 18:56:57</v>
+      </c>
+      <c r="C9" t="str">
+        <v>27-03-2026</v>
+      </c>
+      <c r="D9" t="str">
+        <v>UPI/Indian Railways/608681305456/UPI</v>
+      </c>
+      <c r="E9" t="str">
+        <v>UPI-608668633200</v>
+      </c>
+      <c r="F9" t="str">
+        <v>95</v>
+      </c>
+      <c r="G9" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>27-03-2026 18:26:29</v>
+      </c>
+      <c r="C10" t="str">
+        <v>27-03-2026</v>
+      </c>
+      <c r="D10" t="str">
+        <v>UPI/Mahesh Ramchand/608678800313/UPI</v>
+      </c>
+      <c r="E10" t="str">
+        <v>UPI-608666050537</v>
+      </c>
+      <c r="F10" t="str">
+        <v>20</v>
+      </c>
+      <c r="G10" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>27-03-2026 07:07:52</v>
+      </c>
+      <c r="C11" t="str">
+        <v>27-03-2026</v>
+      </c>
+      <c r="D11" t="str">
+        <v>NACH-ECS-CR-IOCL-30294448</v>
+      </c>
+      <c r="E11" t="str">
+        <v>NACHDB27032600083397</v>
+      </c>
+      <c r="F11" t="str">
+        <v>236</v>
+      </c>
+      <c r="G11" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>25-03-2026 06:39:14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>25-03-2026</v>
+      </c>
+      <c r="D12" t="str">
+        <v>UPI/BAJAJ FINANCE L/102971560082/Mandate Refund</v>
+      </c>
+      <c r="E12" t="str">
+        <v>UPI-608485981811</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>21-03-2026 00:26:47</v>
+      </c>
+      <c r="C13" t="str">
+        <v>21-03-2026</v>
+      </c>
+      <c r="D13" t="str">
+        <v>UPI/BAJAJ FINANCE L/102949504290/Mandate Refund</v>
+      </c>
+      <c r="E13" t="str">
+        <v>UPI-608009712758</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>20-03-2026 09:35:17</v>
+      </c>
+      <c r="C14" t="str">
+        <v>20-03-2026</v>
+      </c>
+      <c r="D14" t="str">
+        <v>UPI/RAJ NILESH BHAR/607922079724/UPI</v>
+      </c>
+      <c r="E14" t="str">
+        <v>UPI-607944620874</v>
+      </c>
+      <c r="F14" t="str">
+        <v>350</v>
+      </c>
+      <c r="G14" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>19-03-2026 17:41:22</v>
+      </c>
+      <c r="C15" t="str">
+        <v>19-03-2026</v>
+      </c>
+      <c r="D15" t="str">
+        <v>UPI/GUPTA ROHIT DIL/607894860566/UPI</v>
+      </c>
+      <c r="E15" t="str">
+        <v>UPI-607805317412</v>
+      </c>
+      <c r="F15" t="str">
+        <v>10</v>
+      </c>
+      <c r="G15" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>15-03-2026 12:59:50</v>
+      </c>
+      <c r="C16" t="str">
+        <v>15-03-2026</v>
+      </c>
+      <c r="D16" t="str">
+        <v>UPI/UPADHYAY SHUBHA/607412785137/UPI</v>
+      </c>
+      <c r="E16" t="str">
+        <v>UPI-607489431565</v>
+      </c>
+      <c r="F16" t="str">
+        <v>41</v>
+      </c>
+      <c r="G16" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>15-03-2026 10:43:18</v>
+      </c>
+      <c r="C17" t="str">
+        <v>15-03-2026</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CASHBACK EARNED</v>
+      </c>
+      <c r="E17" t="str">
+        <v>ONBF-7e36c73996525fa</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>15-03-2026 10:42:56</v>
+      </c>
+      <c r="C18" t="str">
+        <v>15-03-2026</v>
+      </c>
+      <c r="D18" t="str">
+        <v>UPI/Somesh Sanjay S/607410314989/UPI</v>
+      </c>
+      <c r="E18" t="str">
+        <v>UPI-607480327414</v>
+      </c>
+      <c r="F18" t="str">
+        <v>90</v>
+      </c>
+      <c r="G18" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>15-03-2026 10:42:33</v>
+      </c>
+      <c r="C19" t="str">
+        <v>15-03-2026</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CASHBACK EARNED</v>
+      </c>
+      <c r="E19" t="str">
+        <v>ONBF-27be3dfdb3f57bd</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>15-03-2026 10:42:11</v>
+      </c>
+      <c r="C20" t="str">
+        <v>15-03-2026</v>
+      </c>
+      <c r="D20" t="str">
+        <v>UPI/UPADHYAY SHUBHA/607410312856/UPI</v>
+      </c>
+      <c r="E20" t="str">
+        <v>UPI-607480283563</v>
+      </c>
+      <c r="F20" t="str">
+        <v>150</v>
+      </c>
+      <c r="G20" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>23</v>
+      </c>
+      <c r="B21" t="str">
+        <v>12-03-2026 20:16:19</v>
+      </c>
+      <c r="C21" t="str">
+        <v>12-03-2026</v>
+      </c>
+      <c r="D21" t="str">
+        <v>UPI/Sejal Santosh M/607120087660/UPI</v>
+      </c>
+      <c r="E21" t="str">
+        <v>UPI-607101174273</v>
+      </c>
+      <c r="F21" t="str">
+        <v>12</v>
+      </c>
+      <c r="G21" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>12-03-2026 20:16:39</v>
+      </c>
+      <c r="C22" t="str">
+        <v>12-03-2026</v>
+      </c>
+      <c r="D22" t="str">
+        <v>CASHBACK EARNED</v>
+      </c>
+      <c r="E22" t="str">
+        <v>ONBF-71557866089822e</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1.11</v>
+      </c>
+      <c r="G22" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>21</v>
+      </c>
+      <c r="B23" t="str">
+        <v>13-03-2026 20:54:21</v>
+      </c>
+      <c r="C23" t="str">
+        <v>13-03-2026</v>
+      </c>
+      <c r="D23" t="str">
+        <v>UPI/Singh Juse Cent/607223294454/UPI</v>
+      </c>
+      <c r="E23" t="str">
+        <v>UPI-607278203671</v>
+      </c>
+      <c r="F23" t="str">
+        <v>20</v>
+      </c>
+      <c r="G23" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>20</v>
+      </c>
+      <c r="B24" t="str">
+        <v>14-03-2026 09:17:13</v>
+      </c>
+      <c r="C24" t="str">
+        <v>14-03-2026</v>
+      </c>
+      <c r="D24" t="str">
+        <v>UPI/Indian Railways/607332725645/UPI</v>
+      </c>
+      <c r="E24" t="str">
+        <v>UPI-607301190576</v>
+      </c>
+      <c r="F24" t="str">
+        <v>334.65</v>
+      </c>
+      <c r="G24" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>11-03-2026 22:11:55</v>
+      </c>
+      <c r="C25" t="str">
+        <v>11-03-2026</v>
+      </c>
+      <c r="D25" t="str">
+        <v>UPI/GAUTAM SURENDRA/119878439200/UPI</v>
+      </c>
+      <c r="E25" t="str">
+        <v>UPI-607036459168</v>
+      </c>
+      <c r="F25" t="str">
+        <v>3,895.00</v>
+      </c>
+      <c r="G25" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>11-03-2026 22:10:05</v>
+      </c>
+      <c r="C26" t="str">
+        <v>11-03-2026</v>
+      </c>
+      <c r="D26" t="str">
+        <v>UPI/ANGEL ONE SECUR/607011180575/PayingAngelOne</v>
+      </c>
+      <c r="E26" t="str">
+        <v>UPI-607036325540</v>
+      </c>
+      <c r="F26" t="str">
+        <v>22,000.00</v>
+      </c>
+      <c r="G26" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>11-03-2026 22:09:39</v>
+      </c>
+      <c r="C27" t="str">
+        <v>11-03-2026</v>
+      </c>
+      <c r="D27" t="str">
+        <v>UPI/GAUTAM SURENDRA/119878347968/UPI</v>
+      </c>
+      <c r="E27" t="str">
+        <v>UPI-607036288405</v>
+      </c>
+      <c r="F27" t="str">
+        <v>100</v>
+      </c>
+      <c r="G27" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>11-03-2026 21:48:27</v>
+      </c>
+      <c r="C28" t="str">
+        <v>11-03-2026</v>
+      </c>
+      <c r="D28" t="str">
+        <v>UPI/Transport Commi/607009824568/Transport Commi</v>
+      </c>
+      <c r="E28" t="str">
+        <v>UPI-607034594333</v>
+      </c>
+      <c r="F28" t="str">
+        <v>700</v>
+      </c>
+      <c r="G28" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>11-03-2026 20:26:47</v>
+      </c>
+      <c r="C29" t="str">
+        <v>11-03-2026</v>
+      </c>
+      <c r="D29" t="str">
+        <v>UPI/RAKESH BABULAL /607004261042/Pay to BharatPe</v>
+      </c>
+      <c r="E29" t="str">
+        <v>UPI-607027102447</v>
+      </c>
+      <c r="F29" t="str">
+        <v>30</v>
+      </c>
+      <c r="G29" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>10-03-2026 22:06:37</v>
+      </c>
+      <c r="C30" t="str">
+        <v>10-03-2026</v>
+      </c>
+      <c r="D30" t="str">
+        <v>NEFT HDFCH00859444336 DIGITAL ADVANCED SOFTWARE P</v>
+      </c>
+      <c r="E30" t="str">
+        <v>NEFTINW-1518246668</v>
+      </c>
+      <c r="F30" t="str">
+        <v>22,000.00</v>
+      </c>
+      <c r="G30" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>10-03-2026 21:48:53</v>
+      </c>
+      <c r="C31" t="str">
+        <v>10-03-2026</v>
+      </c>
+      <c r="D31" t="str">
+        <v>UPI/SOMESH SANJAY S/606951905411/UPI</v>
+      </c>
+      <c r="E31" t="str">
+        <v>UPI-606957944743</v>
+      </c>
+      <c r="F31" t="str">
+        <v>40</v>
+      </c>
+      <c r="G31" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>09-03-2026 20:53:44</v>
+      </c>
+      <c r="C32" t="str">
+        <v>09-03-2026</v>
+      </c>
+      <c r="D32" t="str">
+        <v>UPI/SANDHYA SURENDR/606888193194/UPI</v>
+      </c>
+      <c r="E32" t="str">
+        <v>UPI-606875899002</v>
+      </c>
+      <c r="F32" t="str">
+        <v>360</v>
+      </c>
+      <c r="G32" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>09-03-2026 20:26:42</v>
+      </c>
+      <c r="C33" t="str">
+        <v>09-03-2026</v>
+      </c>
+      <c r="D33" t="str">
+        <v>UPI/JUMBO KING/606886018807/UPI</v>
+      </c>
+      <c r="E33" t="str">
+        <v>UPI-606873274907</v>
+      </c>
+      <c r="F33" t="str">
+        <v>237</v>
+      </c>
+      <c r="G33" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>09-03-2026 15:14:15</v>
+      </c>
+      <c r="C34" t="str">
+        <v>09-03-2026</v>
+      </c>
+      <c r="D34" t="str">
+        <v>NACH-ECS-CR-COAL INDIA LTD-326028</v>
+      </c>
+      <c r="E34" t="str">
+        <v>NACHDB09032600531284</v>
+      </c>
+      <c r="F34" t="str">
+        <v>517</v>
+      </c>
+      <c r="G34" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>09-03-2026 10:37:04</v>
+      </c>
+      <c r="C35" t="str">
+        <v>09-03-2026</v>
+      </c>
+      <c r="D35" t="str">
+        <v>UPI/Tungareshwar Sw/606842212385/UPI</v>
+      </c>
+      <c r="E35" t="str">
+        <v>UPI-606827031722</v>
+      </c>
+      <c r="F35" t="str">
+        <v>17</v>
+      </c>
+      <c r="G35" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>09-03-2026 4:57:52</v>
+      </c>
+      <c r="C36" t="str">
+        <v>09-03-2026</v>
+      </c>
+      <c r="D36" t="str">
+        <v>UPI/UPADHYAY SHUBHA/001089942965/Pay</v>
+      </c>
+      <c r="E36" t="str">
+        <v>UPI-606815494601</v>
+      </c>
+      <c r="F36" t="str">
+        <v>500</v>
+      </c>
+      <c r="G36" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>08-03-2026 14:00:59</v>
+      </c>
+      <c r="C37" t="str">
+        <v>08-03-2026</v>
+      </c>
+      <c r="D37" t="str">
+        <v>UPI/Google India Di/606703941431/UPI</v>
+      </c>
+      <c r="E37" t="str">
+        <v>UPI-606767178848</v>
+      </c>
+      <c r="F37" t="str">
+        <v>29</v>
+      </c>
+      <c r="G37" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>08-03-2026 13:06:52</v>
+      </c>
+      <c r="C38" t="str">
+        <v>08-03-2026</v>
+      </c>
+      <c r="D38" t="str">
+        <v>UPI/MOHD ASALM IDRI/606700137109/UPI</v>
+      </c>
+      <c r="E38" t="str">
+        <v>UPI-606763186341</v>
+      </c>
+      <c r="F38" t="str">
+        <v>150</v>
+      </c>
+      <c r="G38" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>08-03-2026 12:43:17</v>
+      </c>
+      <c r="C39" t="str">
+        <v>08-03-2026</v>
+      </c>
+      <c r="D39" t="str">
+        <v>UPI/DHARMDEV RAMSAM/606798444217/UPI</v>
+      </c>
+      <c r="E39" t="str">
+        <v>UPI-606761481874</v>
+      </c>
+      <c r="F39" t="str">
+        <v>10</v>
+      </c>
+      <c r="G39" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>08-03-2026 12:42:47</v>
+      </c>
+      <c r="C40" t="str">
+        <v>08-03-2026</v>
+      </c>
+      <c r="D40" t="str">
+        <v>UPI/SOMESH SANJAY S/606798388458/UPI</v>
+      </c>
+      <c r="E40" t="str">
+        <v>UPI-606761446451</v>
+      </c>
+      <c r="F40" t="str">
+        <v>30</v>
+      </c>
+      <c r="G40" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>07-03-2026 20:22:44</v>
+      </c>
+      <c r="C41" t="str">
+        <v>07-03-2026</v>
+      </c>
+      <c r="D41" t="str">
+        <v>UPI/RITESH RAMKRIPA/606670905075/UPI</v>
+      </c>
+      <c r="E41" t="str">
+        <v>UPI-606621977513</v>
+      </c>
+      <c r="F41" t="str">
+        <v>3,000.00</v>
+      </c>
+      <c r="G41" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>07-03-2026 13:06:54</v>
+      </c>
+      <c r="C42" t="str">
+        <v>07-03-2026</v>
+      </c>
+      <c r="D42" t="str">
+        <v>NEFT AXNFCN1274803152 ANGEL ONE LTD DSCNB ACCOUNT</v>
+      </c>
+      <c r="E42" t="str">
+        <v>NEFTINW-1514360871</v>
+      </c>
+      <c r="F42" t="str">
+        <v>86.72</v>
+      </c>
+      <c r="G42" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>04-03-2026 22:18:52</v>
+      </c>
+      <c r="C43" t="str">
+        <v>04-03-2026</v>
+      </c>
+      <c r="D43" t="str">
+        <v>UPI/RITESH RAMKRIPA/881193575028/Payment from Ph</v>
+      </c>
+      <c r="E43" t="str">
+        <v>UPI-606304970672</v>
+      </c>
+      <c r="F43" t="str">
+        <v>100</v>
+      </c>
+      <c r="G43" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>01-03-2026 21:27:58</v>
+      </c>
+      <c r="C44" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D44" t="str">
+        <v>UPI/GAUTAM SURENDRA/606039448862/UPI</v>
+      </c>
+      <c r="E44" t="str">
+        <v>UPI-606070237837</v>
+      </c>
+      <c r="F44" t="str">
+        <v>8,000.00</v>
+      </c>
+      <c r="G44" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>47</v>
+      </c>
+      <c r="B45" t="str">
+        <v>01-03-2026 20:00:34</v>
+      </c>
+      <c r="C45" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D45" t="str">
+        <v>UPI/Guru Krupa Chin/606036750613/UPI</v>
+      </c>
+      <c r="E45" t="str">
+        <v>UPI-606061825791</v>
+      </c>
+      <c r="F45" t="str">
+        <v>100</v>
+      </c>
+      <c r="G45" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>44</v>
+      </c>
+      <c r="B46" t="str">
+        <v>01-03-2026 21:20:50</v>
+      </c>
+      <c r="C46" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D46" t="str">
+        <v>UPI/MYJIO/606021560744/Pay</v>
+      </c>
+      <c r="E46" t="str">
+        <v>UPI-606069643006</v>
+      </c>
+      <c r="F46" t="str">
+        <v>899</v>
+      </c>
+      <c r="G46" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>01-03-2026 20:29:17</v>
+      </c>
+      <c r="C47" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D47" t="str">
+        <v>UPI/MANOJ MADDESHIY/606037204599/UPI</v>
+      </c>
+      <c r="E47" t="str">
+        <v>UPI-606064873258</v>
+      </c>
+      <c r="F47" t="str">
+        <v>20</v>
+      </c>
+      <c r="G47" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>45</v>
+      </c>
+      <c r="B48" t="str">
+        <v>01-03-2026 20:30:52</v>
+      </c>
+      <c r="C48" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D48" t="str">
+        <v>UPI/MR ANIL  KUAMR/606037240720/UPI</v>
+      </c>
+      <c r="E48" t="str">
+        <v>UPI-606065035687</v>
+      </c>
+      <c r="F48" t="str">
+        <v>20</v>
+      </c>
+      <c r="G48" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>01-03-2026 13:35:40</v>
+      </c>
+      <c r="C49" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D49" t="str">
+        <v>UPI/JAGDISH SHANKAR/112463087555/Payment from Ph</v>
+      </c>
+      <c r="E49" t="str">
+        <v>UPI-606029324983</v>
+      </c>
+      <c r="F49" t="str">
+        <v>10,000.00</v>
+      </c>
+      <c r="G49" t="str">
+        <v>CR</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>01-03-2026 13:18:13</v>
+      </c>
+      <c r="C50" t="str">
+        <v>01-03-2026</v>
+      </c>
+      <c r="D50" t="str">
+        <v>UPI/Google India Di/606012124005/UPI</v>
+      </c>
+      <c r="E50" t="str">
+        <v>UPI-606027937073</v>
+      </c>
+      <c r="F50" t="str">
+        <v>29</v>
+      </c>
+      <c r="G50" t="str">
+        <v>DR</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/data/databases/user_1786447244261.xlsx
+++ b/data/databases/user_1786447244261.xlsx
@@ -9,6 +9,8 @@
     <sheet name="Title" sheetId="4" r:id="rId4"/>
     <sheet name="Heads" sheetId="5" r:id="rId5"/>
     <sheet name="Kotak_Bank_1787732907953" sheetId="6" r:id="rId6"/>
+    <sheet name="Bills" sheetId="7" r:id="rId7"/>
+    <sheet name="Cash" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -126,10 +128,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -161,10 +163,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ­ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¼ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ·ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂªÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ³ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¥ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ®ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¤ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ½ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ§ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ´ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ°ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ«ÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -1934,4 +1936,107 @@
     <ignoredError numberStoredAsText="1" sqref="A1:G50"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G1"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>file_name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>url</v>
+      </c>
+      <c r="D1" t="str">
+        <v>remark</v>
+      </c>
+      <c r="E1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="F1" t="str">
+        <v>crt_by</v>
+      </c>
+      <c r="G1" t="str">
+        <v>crt_dt</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>entry_date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>remark</v>
+      </c>
+      <c r="D1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="E1" t="str">
+        <v>dr_cr</v>
+      </c>
+      <c r="F1" t="str">
+        <v>bill_file_name</v>
+      </c>
+      <c r="G1" t="str">
+        <v>bill_url</v>
+      </c>
+      <c r="H1" t="str">
+        <v>crt_by</v>
+      </c>
+      <c r="I1" t="str">
+        <v>crt_dt</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>1788093024842535</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-08-30</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Sign Exp</v>
+      </c>
+      <c r="D2" t="str">
+        <v>1500</v>
+      </c>
+      <c r="E2" t="str">
+        <v>DR</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1788093024836-65072416.jpeg</v>
+      </c>
+      <c r="G2" t="str">
+        <v>/uploads/images/1788093024836-65072416.jpeg</v>
+      </c>
+      <c r="H2" t="str">
+        <v>gautam@gmail.com</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-08-30T12:30:24.842Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+  </ignoredErrors>
+</worksheet>
 </file>